--- a/econ_module/data/h2bb/transport_cost_assumptions.xlsx
+++ b/econ_module/data/h2bb/transport_cost_assumptions.xlsx
@@ -10,7 +10,7 @@
   </mc:AlternateContent>
   <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{984A5EDD-C133-4FC7-9750-F688248931CE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="57480" yWindow="-4725" windowWidth="29040" windowHeight="15720" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="pipeline_collection" sheetId="1" r:id="rId1"/>
